--- a/public/excel/30112024_pricelist.xlsx
+++ b/public/excel/30112024_pricelist.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="114">
   <si>
     <t>Rice</t>
   </si>
@@ -50,10 +50,7 @@
     <t>₹6,400</t>
   </si>
   <si>
-    <t>-0.78%</t>
-  </si>
-  <si>
-    <t>-1.54%</t>
+    <t>0%</t>
   </si>
   <si>
     <t>STEAM (GRADE A+)</t>
@@ -62,12 +59,6 @@
     <t>₹6,450</t>
   </si>
   <si>
-    <t>-0.77%</t>
-  </si>
-  <si>
-    <t>-1.53%</t>
-  </si>
-  <si>
     <t>CREAMY SELLA</t>
   </si>
   <si>
@@ -80,24 +71,12 @@
     <t>₹5,550</t>
   </si>
   <si>
-    <t>-1.12%</t>
-  </si>
-  <si>
-    <t>-7.53%</t>
-  </si>
-  <si>
     <t>₹7,800</t>
   </si>
   <si>
     <t>₹7,850</t>
   </si>
   <si>
-    <t>0%</t>
-  </si>
-  <si>
-    <t>-1.88%</t>
-  </si>
-  <si>
     <t>GOLDEN SELLA (GRADE A+)</t>
   </si>
   <si>
@@ -107,9 +86,6 @@
     <t>₹8,850</t>
   </si>
   <si>
-    <t>-1.4%</t>
-  </si>
-  <si>
     <t>GOLDEN SELLA (GRADE A)</t>
   </si>
   <si>
@@ -119,102 +95,63 @@
     <t>₹8,500</t>
   </si>
   <si>
-    <t>0.3%</t>
-  </si>
-  <si>
     <t>₹8,100</t>
   </si>
   <si>
     <t>₹8,150</t>
   </si>
   <si>
-    <t>-1.22%</t>
-  </si>
-  <si>
     <t>₹8,300</t>
   </si>
   <si>
     <t>₹8,350</t>
   </si>
   <si>
-    <t>-1.48%</t>
-  </si>
-  <si>
     <t>₹7,500</t>
   </si>
   <si>
     <t>₹7,550</t>
   </si>
   <si>
-    <t>-0.66%</t>
-  </si>
-  <si>
-    <t>-3.83%</t>
-  </si>
-  <si>
     <t>₹6,800</t>
   </si>
   <si>
     <t>₹6,850</t>
   </si>
   <si>
-    <t>5.41%</t>
-  </si>
-  <si>
     <t>₹5,750</t>
   </si>
   <si>
     <t>₹5,800</t>
   </si>
   <si>
-    <t>4.52%</t>
-  </si>
-  <si>
     <t>₹6,150</t>
   </si>
   <si>
     <t>₹6,200</t>
   </si>
   <si>
-    <t>0.82%</t>
-  </si>
-  <si>
     <t>₹6,700</t>
   </si>
   <si>
     <t>₹6,750</t>
   </si>
   <si>
-    <t>6.32%</t>
-  </si>
-  <si>
     <t>₹6,300</t>
   </si>
   <si>
-    <t>1.2%</t>
-  </si>
-  <si>
     <t>₹5,700</t>
   </si>
   <si>
-    <t>-3.38%</t>
-  </si>
-  <si>
     <t>MADHYA-PRADESH</t>
   </si>
   <si>
     <t>₹5,650</t>
   </si>
   <si>
-    <t>4.11%</t>
-  </si>
-  <si>
     <t>STEAM</t>
   </si>
   <si>
-    <t>7.6%</t>
-  </si>
-  <si>
     <t>UTTAR-PRADESH</t>
   </si>
   <si>
@@ -224,57 +161,39 @@
     <t>₹6,100</t>
   </si>
   <si>
-    <t>7.08%</t>
-  </si>
-  <si>
     <t>₹5,600</t>
   </si>
   <si>
-    <t>5.63%</t>
-  </si>
-  <si>
     <t>₹7,200</t>
   </si>
   <si>
     <t>₹7,250</t>
   </si>
   <si>
-    <t>-7.67%</t>
-  </si>
-  <si>
     <t>₹7,150</t>
   </si>
   <si>
-    <t>3.61%</t>
-  </si>
-  <si>
     <t>₹7,050</t>
   </si>
   <si>
     <t>₹7,100</t>
   </si>
   <si>
-    <t>-6.6%</t>
-  </si>
-  <si>
     <t>₹6,500</t>
   </si>
   <si>
     <t>₹6,550</t>
   </si>
   <si>
-    <t>-11.53%</t>
-  </si>
-  <si>
-    <t>-11.15%</t>
+    <t>₹6,325</t>
+  </si>
+  <si>
+    <t>-0.98%</t>
   </si>
   <si>
     <t>₹6,600</t>
   </si>
   <si>
-    <t>-7.75%</t>
-  </si>
-  <si>
     <t>PUSA/DB</t>
   </si>
   <si>
@@ -284,12 +203,6 @@
     <t>₹5,100</t>
   </si>
   <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>-6.48%</t>
-  </si>
-  <si>
     <t>RAW (NEW CROP)</t>
   </si>
   <si>
@@ -302,9 +215,6 @@
     <t>₹5,400</t>
   </si>
   <si>
-    <t>-7.76%</t>
-  </si>
-  <si>
     <t>RAW</t>
   </si>
   <si>
@@ -314,9 +224,6 @@
     <t>₹5,150</t>
   </si>
   <si>
-    <t>3.02%</t>
-  </si>
-  <si>
     <t>₹5,850</t>
   </si>
   <si>
@@ -329,18 +236,9 @@
     <t>₹4,800</t>
   </si>
   <si>
-    <t>1.06%</t>
-  </si>
-  <si>
     <t>₹5,025</t>
   </si>
   <si>
-    <t>-0.99%</t>
-  </si>
-  <si>
-    <t>9.56%</t>
-  </si>
-  <si>
     <t>SHARBATI</t>
   </si>
   <si>
@@ -353,15 +251,9 @@
     <t>₹5,350</t>
   </si>
   <si>
-    <t>2.9%</t>
-  </si>
-  <si>
     <t>₹4,900</t>
   </si>
   <si>
-    <t>-1.98%</t>
-  </si>
-  <si>
     <t>₹4,450</t>
   </si>
   <si>
@@ -377,18 +269,12 @@
     <t>₹4,425</t>
   </si>
   <si>
-    <t>-0.56%</t>
-  </si>
-  <si>
     <t>₹4,125</t>
   </si>
   <si>
     <t>₹4,150</t>
   </si>
   <si>
-    <t>-2.07%</t>
-  </si>
-  <si>
     <t>₹4,200</t>
   </si>
   <si>
@@ -401,39 +287,21 @@
     <t>₹4,850</t>
   </si>
   <si>
-    <t>2.09%</t>
-  </si>
-  <si>
     <t>₹4,950</t>
   </si>
   <si>
     <t>₹4,550</t>
   </si>
   <si>
-    <t>-1.08%</t>
-  </si>
-  <si>
-    <t>-2.16%</t>
-  </si>
-  <si>
     <t>RH-10</t>
   </si>
   <si>
-    <t>4.28%</t>
-  </si>
-  <si>
     <t>₹4,350</t>
   </si>
   <si>
-    <t>1.16%</t>
-  </si>
-  <si>
     <t>SONA MANSOORI</t>
   </si>
   <si>
-    <t>-15.13%</t>
-  </si>
-  <si>
     <t>PARMAL</t>
   </si>
   <si>
@@ -473,15 +341,9 @@
     <t>₹3,450</t>
   </si>
   <si>
-    <t>-6.14%</t>
-  </si>
-  <si>
     <t>GOVIND BHOG</t>
   </si>
   <si>
-    <t>-7.8%</t>
-  </si>
-  <si>
     <t>RAW 2 YEAR (OLD)</t>
   </si>
   <si>
@@ -495,9 +357,6 @@
   </si>
   <si>
     <t>RAW (OLD)</t>
-  </si>
-  <si>
-    <t>1.29%</t>
   </si>
 </sst>
 </file>
@@ -917,12 +776,12 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -934,13 +793,13 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -956,25 +815,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>2024</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7">
-        <v>2024</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -990,7 +849,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -999,21 +858,21 @@
         <v>2023</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -1022,21 +881,21 @@
         <v>2023</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -1045,16 +904,16 @@
         <v>2023</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1068,21 +927,21 @@
         <v>2024</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>8</v>
@@ -1091,39 +950,39 @@
         <v>2024</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C15">
         <v>2023</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1139,7 +998,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -1148,21 +1007,21 @@
         <v>2024</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -1171,21 +1030,21 @@
         <v>2024</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
         <v>8</v>
@@ -1194,16 +1053,16 @@
         <v>2024</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1217,21 +1076,21 @@
         <v>2024</v>
       </c>
       <c r="D21" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>8</v>
@@ -1240,131 +1099,131 @@
         <v>2024</v>
       </c>
       <c r="D22" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C23">
         <v>2024</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C24">
         <v>2024</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C25">
         <v>2024</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C26">
         <v>2024</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F26" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C27">
         <v>2024</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F27" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1380,7 +1239,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
         <v>8</v>
@@ -1389,16 +1248,16 @@
         <v>2024</v>
       </c>
       <c r="D30" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F30" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1412,21 +1271,21 @@
         <v>2024</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="F31" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
         <v>8</v>
@@ -1435,21 +1294,21 @@
         <v>2024</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="E32" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
         <v>8</v>
@@ -1458,21 +1317,21 @@
         <v>2024</v>
       </c>
       <c r="D33" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F33" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
         <v>8</v>
@@ -1481,67 +1340,67 @@
         <v>2024</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E34" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F34" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C35">
         <v>2024</v>
       </c>
       <c r="D35" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="G35" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C36">
         <v>2024</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E36" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="2" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1552,79 +1411,79 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39">
+        <v>2024</v>
+      </c>
+      <c r="D39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" t="s">
         <v>61</v>
       </c>
-      <c r="C39">
-        <v>2024</v>
-      </c>
-      <c r="D39" t="s">
-        <v>87</v>
-      </c>
-      <c r="E39" t="s">
-        <v>88</v>
-      </c>
       <c r="F39" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C40">
         <v>2024</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F40" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C41">
         <v>2024</v>
       </c>
       <c r="D41" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="E41" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="F41" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C42">
         <v>2023</v>
@@ -1633,41 +1492,41 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C43">
         <v>2024</v>
       </c>
       <c r="D43" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F43" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1678,7 +1537,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
         <v>8</v>
@@ -1687,21 +1546,21 @@
         <v>2023</v>
       </c>
       <c r="D46" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="E46" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="F46" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -1710,21 +1569,21 @@
         <v>2023</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="F47" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -1733,44 +1592,44 @@
         <v>2023</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="E48" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="F48" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G48" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C49">
         <v>2024</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E49" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="F49" t="s">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1781,7 +1640,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
         <v>8</v>
@@ -1790,90 +1649,90 @@
         <v>2023</v>
       </c>
       <c r="D52" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E52" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="F52" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53">
+        <v>2024</v>
+      </c>
+      <c r="D53" t="s">
         <v>64</v>
       </c>
-      <c r="B53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53">
-        <v>2024</v>
-      </c>
-      <c r="D53" t="s">
-        <v>93</v>
-      </c>
       <c r="E53" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F53" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C54">
         <v>2024</v>
       </c>
       <c r="D54" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E54" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="F54" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C55">
         <v>2023</v>
       </c>
       <c r="D55" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="E55" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="F55" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -1884,7 +1743,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B58" t="s">
         <v>8</v>
@@ -1893,21 +1752,21 @@
         <v>2024</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="F58" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>120</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B59" t="s">
         <v>8</v>
@@ -1916,21 +1775,21 @@
         <v>2024</v>
       </c>
       <c r="D59" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E59" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="F59" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G59" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B60" t="s">
         <v>8</v>
@@ -1939,21 +1798,21 @@
         <v>2024</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="F60" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -1964,7 +1823,7 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
         <v>8</v>
@@ -1973,21 +1832,21 @@
         <v>2023</v>
       </c>
       <c r="D63" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="E63" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="F63" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G63" t="s">
-        <v>128</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B64" t="s">
         <v>8</v>
@@ -1996,21 +1855,21 @@
         <v>2023</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="E64" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="F64" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G64" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
         <v>8</v>
@@ -2019,44 +1878,44 @@
         <v>2023</v>
       </c>
       <c r="D65" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="E65" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F65" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G65" t="s">
-        <v>131</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C66">
         <v>2023</v>
       </c>
       <c r="D66" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="E66" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="F66" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G66" t="s">
-        <v>132</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -2067,7 +1926,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B69" t="s">
         <v>8</v>
@@ -2076,21 +1935,21 @@
         <v>2024</v>
       </c>
       <c r="D69" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="E69" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="F69" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G69" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B70" t="s">
         <v>8</v>
@@ -2099,21 +1958,21 @@
         <v>2024</v>
       </c>
       <c r="D70" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="E70" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="F70" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G70" t="s">
-        <v>134</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B71" t="s">
         <v>8</v>
@@ -2122,44 +1981,44 @@
         <v>2024</v>
       </c>
       <c r="D71" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="E71" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="F71" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G71" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C72">
         <v>2023</v>
       </c>
       <c r="D72" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="F72" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G72" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -2170,30 +2029,30 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B75" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C75">
         <v>2024</v>
       </c>
       <c r="D75" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E75" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="F75" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -2204,99 +2063,99 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="B78" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C78">
         <v>2023</v>
       </c>
       <c r="D78" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="E78" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="F78" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="B79" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C79">
         <v>2023</v>
       </c>
       <c r="D79" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="E79" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="F79" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G79" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="B80" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C80">
         <v>2023</v>
       </c>
       <c r="D80" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="E80" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="F80" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G80" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="B81" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C81">
         <v>2023</v>
       </c>
       <c r="D81" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="E81" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="F81" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G81" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="2" t="s">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -2307,30 +2166,30 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B84" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C84">
         <v>2024</v>
       </c>
       <c r="D84" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="E84" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="F84" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G84" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="2" t="s">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -2341,71 +2200,71 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="B87" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C87">
         <v>2024</v>
       </c>
       <c r="D87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="F87" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G87" t="s">
-        <v>154</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="B88" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>2022</v>
       </c>
       <c r="D88" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="E88" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="F88" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="B89" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="C89">
         <v>2023</v>
       </c>
       <c r="D89" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E89" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G89" t="s">
-        <v>160</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
